--- a/data/break_level.xlsx
+++ b/data/break_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15300"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="_________________" sheetId="1" r:id="rId1"/>
@@ -29,31 +29,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
-    <t>Kr85m</t>
+    <t>KR-85M</t>
   </si>
   <si>
-    <t>Kr88</t>
+    <t>KR-88</t>
   </si>
   <si>
-    <t>Xe133</t>
+    <t>XE-133</t>
   </si>
   <si>
-    <t>Xe135</t>
+    <t>XE-135</t>
   </si>
   <si>
-    <t>I131</t>
+    <t>I-131</t>
   </si>
   <si>
-    <t>I132</t>
+    <t>I-132</t>
   </si>
   <si>
-    <t>I133</t>
+    <t>I-133</t>
   </si>
   <si>
-    <t>I134</t>
+    <t>I-134</t>
   </si>
   <si>
-    <t>I135</t>
+    <t>I-135</t>
   </si>
   <si>
     <t>level</t>
@@ -84,10 +84,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -431,12 +438,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -557,139 +579,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1228,31 +1253,31 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
